--- a/output/pdf_financials_xlsx/RGLD.xlsx
+++ b/output/pdf_financials_xlsx/RGLD.xlsx
@@ -2339,13 +2339,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.03495</v>
+        <v>-0.146704</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.025</v>
+        <v>-0.238717</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>2.263567</v>
+        <v>2.180168</v>
       </c>
     </row>
     <row r="119">
@@ -3399,7 +3399,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>-0.181654</v>
       </c>

--- a/output/pdf_financials_xlsx/RGLD.xlsx
+++ b/output/pdf_financials_xlsx/RGLD.xlsx
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>8.899999999999999e-05</v>
       </c>
     </row>
     <row r="13">
@@ -871,7 +871,7 @@
         <v>-0.358259</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.491275</v>
+        <v>-2.491364</v>
       </c>
     </row>
     <row r="28">
@@ -903,7 +903,7 @@
         <v>-0.358259</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.491275</v>
+        <v>-2.491364</v>
       </c>
     </row>
     <row r="30">
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.04253</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.269383</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.019186</v>
       </c>
     </row>
     <row r="35">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.04253</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.269383</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.019186</v>
       </c>
     </row>
     <row r="37">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.04253</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.269383</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.021398</v>
+        <v>0.002212</v>
       </c>
     </row>
     <row r="49">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">

--- a/output/pdf_financials_xlsx/RGLD.xlsx
+++ b/output/pdf_financials_xlsx/RGLD.xlsx
@@ -2067,13 +2067,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.002114</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.024299</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.034268</v>
       </c>
     </row>
     <row r="102">
@@ -2147,13 +2147,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-5.3e-05</v>
+        <v>0.002061</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.009705</v>
+        <v>-0.014594</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.000492</v>
+        <v>0.03476</v>
       </c>
     </row>
     <row r="107">
@@ -3306,7 +3306,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>0.002114</v>
       </c>
